--- a/0.EJEMPLOS_EXAMPLES/FastTest PlugIn - DataBase_Examples - Spanish.xlsx
+++ b/0.EJEMPLOS_EXAMPLES/FastTest PlugIn - DataBase_Examples - Spanish.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28422"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milag\Desktop\FTP_81\1. EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AHGM\0. GITHUB\FTP_Privado\0.EJEMPLOS_EXAMPLES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0281B5-E1EC-49DD-9903-D8A05CD886BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A622233-A274-435F-92D0-ACDA7C50F439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -630,7 +630,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="972">
   <si>
     <t>MILAGROS HUERTA GÓMEZ DE MERODIO</t>
   </si>
@@ -3194,9 +3194,6 @@
 默认情况下，根据您要使用的语言编写相应的数字。 您可以随时更改它。</t>
   </si>
   <si>
-    <t>V - 7.8  - 02/04/2023</t>
-  </si>
-  <si>
     <t>Atención a la lectura</t>
   </si>
   <si>
@@ -3248,21 +3245,6 @@
     <t>m</t>
   </si>
   <si>
-    <t>m^{^2^}^</t>
-  </si>
-  <si>
-    <t>m^{^3^}^</t>
-  </si>
-  <si>
-    <t>m^{^4^}^</t>
-  </si>
-  <si>
-    <t>m_{_2_}_</t>
-  </si>
-  <si>
-    <t>m_{_3_}_</t>
-  </si>
-  <si>
     <t>MATEMÁTICAS</t>
   </si>
   <si>
@@ -3285,12 +3267,6 @@
   </si>
   <si>
     <t>mm</t>
-  </si>
-  <si>
-    <t>mm^{^2^}^</t>
-  </si>
-  <si>
-    <t>mm^{^3^}^</t>
   </si>
   <si>
     <t>El caballo Blanco de Santiago es BLANCO</t>
@@ -3613,15 +3589,39 @@
     <t>Imágenes y Formulas</t>
   </si>
   <si>
-    <t>Selecciona la fórmula correcta: [[[{1:MCVS:~%100%\(\frac{\cos^2(x)\}{x-1\}\)#OK~%0%\(-\frac{\cos^2(x)\}{x-1\}\)#~%0%\(\frac{\cos(x)\}{x-1\}-\frac{\sin(x)\}{(x-1)^2\}\)#}]]]&lt;br&gt;
-Selecciona la imágen correcta: [[[{1:MCVS:~%100%&lt;img src = "https://dl.dropboxusercontent.com/s/oh1ssro2fay57yo/Alumno_hablando_rapido.gif" width = "" height = "100"&gt;#OK~%0%&lt;img src = "https://dl.dropboxusercontent.com/s/2smr0aec6oujybp/Antonio_hablando_izq_rapido.gif" width = "" height = "120"&gt;#NO~%0%&lt;img src = "https://dl.dropboxusercontent.com/s/qfxkf5guj4pjibp/Profe_hablando_rapido.gif" width = "" height = "100"&gt;#NO}]]]</t>
-  </si>
-  <si>
     <t>Fórmulas</t>
   </si>
   <si>
     <t>Selecciona la fórmula correcta: &lt;br&gt;
 {1:MCHS:~%100%\(\frac{\cos^2(x)\}{x-1\}\)#~%0%\(-\frac{\cos^2(x)\}{x-1\}\)#}&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>[[[Selecciona la fórmula correcta: {1:MCVS:~%100%\(\frac{\cos^2(x)\}{x-1\}\)#OK~%0%\(-\frac{\cos^2(x)\}{x-1\}\)#~%0%\(\frac{\cos(x)\}{x-1\}-\frac{\sin(x)\}{(x-1)^2\}\)#}]]]&lt;br&gt;
+Selecciona la imágen correcta: [[[{1:MCVS:~%100%&lt;img src = "https://dl.dropboxusercontent.com/s/oh1ssro2fay57yo/Alumno_hablando_rapido.gif" width = "" height = "100"&gt;#OK~%0%&lt;img src = "https://dl.dropboxusercontent.com/s/2smr0aec6oujybp/Antonio_hablando_izq_rapido.gif" width = "" height = "120"&gt;#NO~%0%&lt;img src = "https://dl.dropboxusercontent.com/s/qfxkf5guj4pjibp/Profe_hablando_rapido.gif" width = "" height = "100"&gt;#NO}]]]</t>
+  </si>
+  <si>
+    <t>V - 8.3 - 02/01/2025</t>
+  </si>
+  <si>
+    <t>m²</t>
+  </si>
+  <si>
+    <t>m³</t>
+  </si>
+  <si>
+    <t>m⁴</t>
+  </si>
+  <si>
+    <t>m₂</t>
+  </si>
+  <si>
+    <t>m₃</t>
+  </si>
+  <si>
+    <t>mm²</t>
+  </si>
+  <si>
+    <t>mm⁴</t>
   </si>
 </sst>
 </file>
@@ -4480,7 +4480,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="278">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5250,6 +5250,65 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5272,9 +5331,6 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5290,95 +5346,18 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="348">
@@ -21687,7 +21666,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja_00"/>
   <dimension ref="A1:T47"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" zeroHeight="1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" zeroHeight="1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10.64453125" customWidth="1"/>
     <col min="2" max="2" width="2.64453125" customWidth="1"/>
@@ -21697,32 +21676,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="28.7" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="243" t="s">
+      <c r="A1" s="263" t="s">
         <v>387</v>
       </c>
-      <c r="B1" s="262" t="s">
+      <c r="B1" s="253" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="263"/>
-      <c r="D1" s="263"/>
-      <c r="E1" s="263"/>
-      <c r="F1" s="263"/>
-      <c r="G1" s="263"/>
-      <c r="H1" s="263"/>
-      <c r="I1" s="263"/>
-      <c r="J1" s="263"/>
-      <c r="K1" s="263"/>
-      <c r="L1" s="263"/>
-      <c r="M1" s="263"/>
-      <c r="N1" s="263"/>
-      <c r="O1" s="263"/>
-      <c r="P1" s="263"/>
-      <c r="Q1" s="263"/>
-      <c r="R1" s="263"/>
-      <c r="S1" s="264"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="254"/>
+      <c r="F1" s="254"/>
+      <c r="G1" s="254"/>
+      <c r="H1" s="254"/>
+      <c r="I1" s="254"/>
+      <c r="J1" s="254"/>
+      <c r="K1" s="254"/>
+      <c r="L1" s="254"/>
+      <c r="M1" s="254"/>
+      <c r="N1" s="254"/>
+      <c r="O1" s="254"/>
+      <c r="P1" s="254"/>
+      <c r="Q1" s="254"/>
+      <c r="R1" s="254"/>
+      <c r="S1" s="255"/>
     </row>
     <row r="2" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="244"/>
+      <c r="A2" s="264"/>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -21743,23 +21722,23 @@
       <c r="S2" s="6"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A3" s="244"/>
+      <c r="A3" s="264"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
-      <c r="G3" s="251" t="str">
+      <c r="G3" s="270" t="str">
         <f ca="1">INDIRECT("Z_IN_04_"&amp;IDIOMA)</f>
         <v>Esta Aplicación ha sido desarrollada, en la primera versión, por:</v>
       </c>
-      <c r="H3" s="251"/>
-      <c r="I3" s="251"/>
-      <c r="J3" s="251"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="251"/>
-      <c r="M3" s="251"/>
-      <c r="N3" s="251"/>
+      <c r="H3" s="270"/>
+      <c r="I3" s="270"/>
+      <c r="J3" s="270"/>
+      <c r="K3" s="270"/>
+      <c r="L3" s="270"/>
+      <c r="M3" s="270"/>
+      <c r="N3" s="270"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
@@ -21767,7 +21746,7 @@
       <c r="S3" s="6"/>
     </row>
     <row r="4" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="244"/>
+      <c r="A4" s="264"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -21788,125 +21767,125 @@
       <c r="S4" s="6"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="244"/>
+      <c r="A5" s="264"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="268"/>
-      <c r="G5" s="268"/>
+      <c r="F5" s="261"/>
+      <c r="G5" s="261"/>
       <c r="H5" s="134"/>
-      <c r="I5" s="252" t="s">
+      <c r="I5" s="271" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="252"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="252"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="250"/>
-      <c r="O5" s="250"/>
-      <c r="P5" s="269" t="s">
+      <c r="N5" s="245"/>
+      <c r="O5" s="245"/>
+      <c r="P5" s="262" t="s">
         <v>651</v>
       </c>
-      <c r="Q5" s="269"/>
-      <c r="R5" s="269"/>
+      <c r="Q5" s="262"/>
+      <c r="R5" s="262"/>
       <c r="S5" s="6"/>
     </row>
     <row r="6" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="244"/>
+      <c r="A6" s="264"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="268"/>
-      <c r="G6" s="268"/>
+      <c r="F6" s="261"/>
+      <c r="G6" s="261"/>
       <c r="H6" s="134"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
-      <c r="N6" s="250"/>
-      <c r="O6" s="250"/>
-      <c r="P6" s="254" t="str">
+      <c r="N6" s="245"/>
+      <c r="O6" s="245"/>
+      <c r="P6" s="273" t="str">
         <f ca="1">INDIRECT("Z_IN_01_"&amp;IDIOMA)</f>
         <v>CANAL YOUTUBE</v>
       </c>
-      <c r="Q6" s="254"/>
-      <c r="R6" s="254"/>
+      <c r="Q6" s="273"/>
+      <c r="R6" s="273"/>
       <c r="S6" s="6"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="244"/>
+      <c r="A7" s="264"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="268"/>
-      <c r="G7" s="268"/>
+      <c r="F7" s="261"/>
+      <c r="G7" s="261"/>
       <c r="H7" s="134"/>
-      <c r="I7" s="251" t="str">
+      <c r="I7" s="270" t="str">
         <f ca="1">INDIRECT("Z_IN_05_"&amp;IDIOMA)</f>
         <v>Universidad de Cádiz</v>
       </c>
-      <c r="J7" s="251"/>
-      <c r="K7" s="251"/>
-      <c r="L7" s="251"/>
+      <c r="J7" s="270"/>
+      <c r="K7" s="270"/>
+      <c r="L7" s="270"/>
       <c r="M7" s="5"/>
-      <c r="N7" s="250"/>
-      <c r="O7" s="250"/>
-      <c r="P7" s="254"/>
-      <c r="Q7" s="254"/>
-      <c r="R7" s="254"/>
+      <c r="N7" s="245"/>
+      <c r="O7" s="245"/>
+      <c r="P7" s="273"/>
+      <c r="Q7" s="273"/>
+      <c r="R7" s="273"/>
       <c r="S7" s="6"/>
     </row>
     <row r="8" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="244"/>
+      <c r="A8" s="264"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="268"/>
-      <c r="G8" s="268"/>
+      <c r="F8" s="261"/>
+      <c r="G8" s="261"/>
       <c r="H8" s="134"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="250"/>
-      <c r="O8" s="250"/>
+      <c r="N8" s="245"/>
+      <c r="O8" s="245"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="6"/>
     </row>
     <row r="9" spans="1:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="245"/>
+      <c r="A9" s="265"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="265" t="str">
+      <c r="C9" s="256" t="str">
         <f ca="1">INDIRECT("Z_IN_03_"&amp;IDIOMA)</f>
         <v>LEER CON ATENCIÓN</v>
       </c>
-      <c r="D9" s="265"/>
+      <c r="D9" s="256"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="268"/>
-      <c r="G9" s="268"/>
+      <c r="F9" s="261"/>
+      <c r="G9" s="261"/>
       <c r="H9" s="134"/>
-      <c r="I9" s="253" t="s">
+      <c r="I9" s="272" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="253"/>
-      <c r="K9" s="253"/>
-      <c r="L9" s="253"/>
+      <c r="J9" s="272"/>
+      <c r="K9" s="272"/>
+      <c r="L9" s="272"/>
       <c r="M9" s="5"/>
-      <c r="N9" s="250"/>
-      <c r="O9" s="250"/>
-      <c r="P9" s="255" t="s">
-        <v>831</v>
-      </c>
-      <c r="Q9" s="255"/>
-      <c r="R9" s="255"/>
+      <c r="N9" s="245"/>
+      <c r="O9" s="245"/>
+      <c r="P9" s="274" t="s">
+        <v>964</v>
+      </c>
+      <c r="Q9" s="274"/>
+      <c r="R9" s="274"/>
       <c r="S9" s="6"/>
     </row>
     <row r="10" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
@@ -21914,256 +21893,256 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="268"/>
-      <c r="G10" s="268"/>
+      <c r="F10" s="261"/>
+      <c r="G10" s="261"/>
       <c r="H10" s="134"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="250"/>
-      <c r="O10" s="250"/>
+      <c r="N10" s="245"/>
+      <c r="O10" s="245"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="6"/>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="246" t="s">
+      <c r="A11" s="266" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="266" t="str">
+      <c r="D11" s="257" t="str">
         <f ca="1">INDIRECT("Z_IN_06_"&amp;IDIOMA)</f>
         <v>1. Esta aplicación se ha desarrollado gracias a un Proyecto de Innovación Docente aprobado por la Unidad de Innovación Docente de la Universidad de Cádiz.
 2. El usuario final es aquel docente que quiera usar los CUESTIONARIOS de la plataforma Moodle. También la puede usar quien quiera tener sus Bancos de Preguntas almacenados en un mismo sitio y con orden.
 3. La aplicación sirve para facilitar la creación de un BANCO DE PREGUNTAS para los cuestionarios, el usuario final deberá repasar que las preguntas se importan bien (al menos las primeras veces) así como si ha rellenado los datos de manera adecuada, como si lo estuviera haciendo en Moodle.
 Pulsa sobre el TIPO DE PREGUNTA sobre el que quieres CONSULTAR las preguntas almacenadas.</v>
       </c>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="266"/>
-      <c r="L11" s="266"/>
-      <c r="M11" s="266"/>
-      <c r="N11" s="266"/>
-      <c r="O11" s="266"/>
-      <c r="P11" s="266"/>
-      <c r="Q11" s="266"/>
-      <c r="R11" s="266"/>
+      <c r="E11" s="257"/>
+      <c r="F11" s="257"/>
+      <c r="G11" s="257"/>
+      <c r="H11" s="257"/>
+      <c r="I11" s="257"/>
+      <c r="J11" s="257"/>
+      <c r="K11" s="257"/>
+      <c r="L11" s="257"/>
+      <c r="M11" s="257"/>
+      <c r="N11" s="257"/>
+      <c r="O11" s="257"/>
+      <c r="P11" s="257"/>
+      <c r="Q11" s="257"/>
+      <c r="R11" s="257"/>
       <c r="S11" s="6"/>
     </row>
     <row r="12" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="246"/>
+      <c r="A12" s="266"/>
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
-      <c r="D12" s="266"/>
-      <c r="E12" s="266"/>
-      <c r="F12" s="266"/>
-      <c r="G12" s="266"/>
-      <c r="H12" s="266"/>
-      <c r="I12" s="266"/>
-      <c r="J12" s="266"/>
-      <c r="K12" s="266"/>
-      <c r="L12" s="266"/>
-      <c r="M12" s="266"/>
-      <c r="N12" s="266"/>
-      <c r="O12" s="266"/>
-      <c r="P12" s="266"/>
-      <c r="Q12" s="266"/>
-      <c r="R12" s="266"/>
+      <c r="D12" s="257"/>
+      <c r="E12" s="257"/>
+      <c r="F12" s="257"/>
+      <c r="G12" s="257"/>
+      <c r="H12" s="257"/>
+      <c r="I12" s="257"/>
+      <c r="J12" s="257"/>
+      <c r="K12" s="257"/>
+      <c r="L12" s="257"/>
+      <c r="M12" s="257"/>
+      <c r="N12" s="257"/>
+      <c r="O12" s="257"/>
+      <c r="P12" s="257"/>
+      <c r="Q12" s="257"/>
+      <c r="R12" s="257"/>
       <c r="S12" s="6"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A13" s="246"/>
+      <c r="A13" s="266"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="266"/>
-      <c r="E13" s="266"/>
-      <c r="F13" s="266"/>
-      <c r="G13" s="266"/>
-      <c r="H13" s="266"/>
-      <c r="I13" s="266"/>
-      <c r="J13" s="266"/>
-      <c r="K13" s="266"/>
-      <c r="L13" s="266"/>
-      <c r="M13" s="266"/>
-      <c r="N13" s="266"/>
-      <c r="O13" s="266"/>
-      <c r="P13" s="266"/>
-      <c r="Q13" s="266"/>
-      <c r="R13" s="266"/>
+      <c r="D13" s="257"/>
+      <c r="E13" s="257"/>
+      <c r="F13" s="257"/>
+      <c r="G13" s="257"/>
+      <c r="H13" s="257"/>
+      <c r="I13" s="257"/>
+      <c r="J13" s="257"/>
+      <c r="K13" s="257"/>
+      <c r="L13" s="257"/>
+      <c r="M13" s="257"/>
+      <c r="N13" s="257"/>
+      <c r="O13" s="257"/>
+      <c r="P13" s="257"/>
+      <c r="Q13" s="257"/>
+      <c r="R13" s="257"/>
       <c r="S13" s="6"/>
     </row>
     <row r="14" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
-      <c r="D14" s="266"/>
-      <c r="E14" s="266"/>
-      <c r="F14" s="266"/>
-      <c r="G14" s="266"/>
-      <c r="H14" s="266"/>
-      <c r="I14" s="266"/>
-      <c r="J14" s="266"/>
-      <c r="K14" s="266"/>
-      <c r="L14" s="266"/>
-      <c r="M14" s="266"/>
-      <c r="N14" s="266"/>
-      <c r="O14" s="266"/>
-      <c r="P14" s="266"/>
-      <c r="Q14" s="266"/>
-      <c r="R14" s="266"/>
+      <c r="D14" s="257"/>
+      <c r="E14" s="257"/>
+      <c r="F14" s="257"/>
+      <c r="G14" s="257"/>
+      <c r="H14" s="257"/>
+      <c r="I14" s="257"/>
+      <c r="J14" s="257"/>
+      <c r="K14" s="257"/>
+      <c r="L14" s="257"/>
+      <c r="M14" s="257"/>
+      <c r="N14" s="257"/>
+      <c r="O14" s="257"/>
+      <c r="P14" s="257"/>
+      <c r="Q14" s="257"/>
+      <c r="R14" s="257"/>
       <c r="S14" s="6"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
-      <c r="D15" s="266"/>
-      <c r="E15" s="266"/>
-      <c r="F15" s="266"/>
-      <c r="G15" s="266"/>
-      <c r="H15" s="266"/>
-      <c r="I15" s="266"/>
-      <c r="J15" s="266"/>
-      <c r="K15" s="266"/>
-      <c r="L15" s="266"/>
-      <c r="M15" s="266"/>
-      <c r="N15" s="266"/>
-      <c r="O15" s="266"/>
-      <c r="P15" s="266"/>
-      <c r="Q15" s="266"/>
-      <c r="R15" s="266"/>
+      <c r="D15" s="257"/>
+      <c r="E15" s="257"/>
+      <c r="F15" s="257"/>
+      <c r="G15" s="257"/>
+      <c r="H15" s="257"/>
+      <c r="I15" s="257"/>
+      <c r="J15" s="257"/>
+      <c r="K15" s="257"/>
+      <c r="L15" s="257"/>
+      <c r="M15" s="257"/>
+      <c r="N15" s="257"/>
+      <c r="O15" s="257"/>
+      <c r="P15" s="257"/>
+      <c r="Q15" s="257"/>
+      <c r="R15" s="257"/>
       <c r="S15" s="6"/>
     </row>
     <row r="16" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
-      <c r="D16" s="266"/>
-      <c r="E16" s="266"/>
-      <c r="F16" s="266"/>
-      <c r="G16" s="266"/>
-      <c r="H16" s="266"/>
-      <c r="I16" s="266"/>
-      <c r="J16" s="266"/>
-      <c r="K16" s="266"/>
-      <c r="L16" s="266"/>
-      <c r="M16" s="266"/>
-      <c r="N16" s="266"/>
-      <c r="O16" s="266"/>
-      <c r="P16" s="266"/>
-      <c r="Q16" s="266"/>
-      <c r="R16" s="266"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="257"/>
+      <c r="F16" s="257"/>
+      <c r="G16" s="257"/>
+      <c r="H16" s="257"/>
+      <c r="I16" s="257"/>
+      <c r="J16" s="257"/>
+      <c r="K16" s="257"/>
+      <c r="L16" s="257"/>
+      <c r="M16" s="257"/>
+      <c r="N16" s="257"/>
+      <c r="O16" s="257"/>
+      <c r="P16" s="257"/>
+      <c r="Q16" s="257"/>
+      <c r="R16" s="257"/>
       <c r="S16" s="6"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A17" s="247" t="str">
+      <c r="A17" s="267" t="str">
         <f>IFERROR(HLOOKUP(LANGUAGE,DICCIONARIO!F1:K20,20,0),LANGUAGE)</f>
         <v>PERSONALIZAR DICCIONARIO</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="266"/>
-      <c r="E17" s="266"/>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="266"/>
-      <c r="J17" s="266"/>
-      <c r="K17" s="266"/>
-      <c r="L17" s="266"/>
-      <c r="M17" s="266"/>
-      <c r="N17" s="266"/>
-      <c r="O17" s="266"/>
-      <c r="P17" s="266"/>
-      <c r="Q17" s="266"/>
-      <c r="R17" s="266"/>
+      <c r="D17" s="257"/>
+      <c r="E17" s="257"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
+      <c r="J17" s="257"/>
+      <c r="K17" s="257"/>
+      <c r="L17" s="257"/>
+      <c r="M17" s="257"/>
+      <c r="N17" s="257"/>
+      <c r="O17" s="257"/>
+      <c r="P17" s="257"/>
+      <c r="Q17" s="257"/>
+      <c r="R17" s="257"/>
       <c r="S17" s="6"/>
     </row>
     <row r="18" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="247"/>
+      <c r="A18" s="267"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
-      <c r="M18" s="266"/>
-      <c r="N18" s="266"/>
-      <c r="O18" s="266"/>
-      <c r="P18" s="266"/>
-      <c r="Q18" s="266"/>
-      <c r="R18" s="266"/>
+      <c r="D18" s="257"/>
+      <c r="E18" s="257"/>
+      <c r="F18" s="257"/>
+      <c r="G18" s="257"/>
+      <c r="H18" s="257"/>
+      <c r="I18" s="257"/>
+      <c r="J18" s="257"/>
+      <c r="K18" s="257"/>
+      <c r="L18" s="257"/>
+      <c r="M18" s="257"/>
+      <c r="N18" s="257"/>
+      <c r="O18" s="257"/>
+      <c r="P18" s="257"/>
+      <c r="Q18" s="257"/>
+      <c r="R18" s="257"/>
       <c r="S18" s="6"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A19" s="247"/>
+      <c r="A19" s="267"/>
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="266"/>
-      <c r="E19" s="266"/>
-      <c r="F19" s="266"/>
-      <c r="G19" s="266"/>
-      <c r="H19" s="266"/>
-      <c r="I19" s="266"/>
-      <c r="J19" s="266"/>
-      <c r="K19" s="266"/>
-      <c r="L19" s="266"/>
-      <c r="M19" s="266"/>
-      <c r="N19" s="266"/>
-      <c r="O19" s="266"/>
-      <c r="P19" s="266"/>
-      <c r="Q19" s="266"/>
-      <c r="R19" s="266"/>
+      <c r="D19" s="257"/>
+      <c r="E19" s="257"/>
+      <c r="F19" s="257"/>
+      <c r="G19" s="257"/>
+      <c r="H19" s="257"/>
+      <c r="I19" s="257"/>
+      <c r="J19" s="257"/>
+      <c r="K19" s="257"/>
+      <c r="L19" s="257"/>
+      <c r="M19" s="257"/>
+      <c r="N19" s="257"/>
+      <c r="O19" s="257"/>
+      <c r="P19" s="257"/>
+      <c r="Q19" s="257"/>
+      <c r="R19" s="257"/>
       <c r="S19" s="6"/>
     </row>
     <row r="20" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="266"/>
-      <c r="E20" s="266"/>
-      <c r="F20" s="266"/>
-      <c r="G20" s="266"/>
-      <c r="H20" s="266"/>
-      <c r="I20" s="266"/>
-      <c r="J20" s="266"/>
-      <c r="K20" s="266"/>
-      <c r="L20" s="266"/>
-      <c r="M20" s="266"/>
-      <c r="N20" s="266"/>
-      <c r="O20" s="266"/>
-      <c r="P20" s="266"/>
-      <c r="Q20" s="266"/>
-      <c r="R20" s="266"/>
+      <c r="D20" s="257"/>
+      <c r="E20" s="257"/>
+      <c r="F20" s="257"/>
+      <c r="G20" s="257"/>
+      <c r="H20" s="257"/>
+      <c r="I20" s="257"/>
+      <c r="J20" s="257"/>
+      <c r="K20" s="257"/>
+      <c r="L20" s="257"/>
+      <c r="M20" s="257"/>
+      <c r="N20" s="257"/>
+      <c r="O20" s="257"/>
+      <c r="P20" s="257"/>
+      <c r="Q20" s="257"/>
+      <c r="R20" s="257"/>
       <c r="S20" s="6"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="266"/>
-      <c r="E21" s="266"/>
-      <c r="F21" s="266"/>
-      <c r="G21" s="266"/>
-      <c r="H21" s="266"/>
-      <c r="I21" s="266"/>
-      <c r="J21" s="266"/>
-      <c r="K21" s="266"/>
-      <c r="L21" s="266"/>
-      <c r="M21" s="266"/>
-      <c r="N21" s="266"/>
-      <c r="O21" s="266"/>
-      <c r="P21" s="266"/>
-      <c r="Q21" s="266"/>
-      <c r="R21" s="266"/>
+      <c r="D21" s="257"/>
+      <c r="E21" s="257"/>
+      <c r="F21" s="257"/>
+      <c r="G21" s="257"/>
+      <c r="H21" s="257"/>
+      <c r="I21" s="257"/>
+      <c r="J21" s="257"/>
+      <c r="K21" s="257"/>
+      <c r="L21" s="257"/>
+      <c r="M21" s="257"/>
+      <c r="N21" s="257"/>
+      <c r="O21" s="257"/>
+      <c r="P21" s="257"/>
+      <c r="Q21" s="257"/>
+      <c r="R21" s="257"/>
       <c r="S21" s="6"/>
     </row>
     <row r="22" spans="1:19" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -22188,172 +22167,172 @@
     </row>
     <row r="23" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="4"/>
-      <c r="C23" s="256" t="str">
+      <c r="C23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_10_"&amp;IDIOMA)</f>
         <v>OM 1R</v>
       </c>
-      <c r="D23" s="267"/>
-      <c r="E23" s="256" t="str">
+      <c r="D23" s="259"/>
+      <c r="E23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_11_"&amp;IDIOMA)</f>
         <v>OM +R</v>
       </c>
-      <c r="F23" s="257"/>
-      <c r="G23" s="256" t="str">
+      <c r="F23" s="260"/>
+      <c r="G23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_12_"&amp;IDIOMA)</f>
         <v>VF</v>
       </c>
-      <c r="H23" s="257"/>
-      <c r="I23" s="256" t="str">
+      <c r="H23" s="260"/>
+      <c r="I23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_13_"&amp;IDIOMA)</f>
         <v>EM</v>
       </c>
-      <c r="J23" s="267"/>
-      <c r="K23" s="256" t="str">
+      <c r="J23" s="259"/>
+      <c r="K23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_14_"&amp;IDIOMA)</f>
         <v>RC</v>
       </c>
-      <c r="L23" s="257"/>
-      <c r="M23" s="256" t="str">
+      <c r="L23" s="260"/>
+      <c r="M23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_15_"&amp;IDIOMA)</f>
         <v>PP</v>
       </c>
-      <c r="N23" s="257"/>
-      <c r="O23" s="256" t="str">
+      <c r="N23" s="260"/>
+      <c r="O23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_31_"&amp;IDIOMA)</f>
         <v>EN</v>
       </c>
-      <c r="P23" s="257"/>
-      <c r="Q23" s="256" t="str">
+      <c r="P23" s="260"/>
+      <c r="Q23" s="258" t="str">
         <f ca="1">INDIRECT("Z_BP_16_"&amp;IDIOMA)</f>
         <v>CL</v>
       </c>
-      <c r="R23" s="257"/>
+      <c r="R23" s="260"/>
       <c r="S23" s="6"/>
     </row>
     <row r="24" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B24" s="4"/>
-      <c r="C24" s="273" t="str">
+      <c r="C24" s="249" t="str">
         <f ca="1">INDIRECT("Z_IN_08_"&amp;IDIOMA)</f>
         <v xml:space="preserve">Opción Múltiple 1R </v>
       </c>
-      <c r="D24" s="258"/>
-      <c r="E24" s="258" t="str">
+      <c r="D24" s="250"/>
+      <c r="E24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_09_"&amp;IDIOMA)</f>
         <v xml:space="preserve">Opción Múltiple +R </v>
       </c>
-      <c r="F24" s="258"/>
-      <c r="G24" s="258" t="str">
+      <c r="F24" s="250"/>
+      <c r="G24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_10_"&amp;IDIOMA)</f>
         <v>Verdadero/Falso</v>
       </c>
-      <c r="H24" s="258"/>
-      <c r="I24" s="258" t="str">
+      <c r="H24" s="250"/>
+      <c r="I24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_11_"&amp;IDIOMA)</f>
         <v>Emparejar</v>
       </c>
-      <c r="J24" s="258"/>
-      <c r="K24" s="258" t="str">
+      <c r="J24" s="250"/>
+      <c r="K24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_12_"&amp;IDIOMA)</f>
         <v>Respuesta Corta</v>
       </c>
-      <c r="L24" s="258"/>
-      <c r="M24" s="258" t="str">
+      <c r="L24" s="250"/>
+      <c r="M24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_13_"&amp;IDIOMA)</f>
         <v>Palabra Perdida</v>
       </c>
-      <c r="N24" s="258"/>
-      <c r="O24" s="258" t="str">
+      <c r="N24" s="250"/>
+      <c r="O24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_16_"&amp;IDIOMA)</f>
         <v>Ensayo</v>
       </c>
-      <c r="P24" s="258"/>
-      <c r="Q24" s="258" t="str">
+      <c r="P24" s="250"/>
+      <c r="Q24" s="250" t="str">
         <f ca="1">INDIRECT("Z_IN_14_"&amp;IDIOMA)</f>
         <v>Cloze</v>
       </c>
-      <c r="R24" s="260"/>
+      <c r="R24" s="275"/>
       <c r="S24" s="6"/>
     </row>
     <row r="25" spans="1:19" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="4"/>
-      <c r="C25" s="274"/>
-      <c r="D25" s="259"/>
-      <c r="E25" s="259"/>
-      <c r="F25" s="259"/>
-      <c r="G25" s="259"/>
-      <c r="H25" s="259"/>
-      <c r="I25" s="259"/>
-      <c r="J25" s="259"/>
-      <c r="K25" s="259"/>
-      <c r="L25" s="259"/>
-      <c r="M25" s="259"/>
-      <c r="N25" s="259"/>
-      <c r="O25" s="259"/>
-      <c r="P25" s="259"/>
-      <c r="Q25" s="259"/>
-      <c r="R25" s="261"/>
+      <c r="C25" s="251"/>
+      <c r="D25" s="252"/>
+      <c r="E25" s="252"/>
+      <c r="F25" s="252"/>
+      <c r="G25" s="252"/>
+      <c r="H25" s="252"/>
+      <c r="I25" s="252"/>
+      <c r="J25" s="252"/>
+      <c r="K25" s="252"/>
+      <c r="L25" s="252"/>
+      <c r="M25" s="252"/>
+      <c r="N25" s="252"/>
+      <c r="O25" s="252"/>
+      <c r="P25" s="252"/>
+      <c r="Q25" s="252"/>
+      <c r="R25" s="276"/>
       <c r="S25" s="6"/>
     </row>
     <row r="26" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="4"/>
-      <c r="C26" s="270" t="str">
+      <c r="C26" s="246" t="str">
         <f ca="1">'Datos OM'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>3 Preguntas</v>
       </c>
-      <c r="D26" s="272"/>
-      <c r="E26" s="270" t="str">
+      <c r="D26" s="248"/>
+      <c r="E26" s="246" t="str">
         <f ca="1">'Datos O2'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>2 Preguntas</v>
       </c>
-      <c r="F26" s="271"/>
-      <c r="G26" s="270" t="str">
+      <c r="F26" s="247"/>
+      <c r="G26" s="246" t="str">
         <f ca="1">'Datos VF'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>2 Preguntas</v>
       </c>
-      <c r="H26" s="271"/>
-      <c r="I26" s="270" t="str">
+      <c r="H26" s="247"/>
+      <c r="I26" s="246" t="str">
         <f ca="1">'Datos EM'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>3 Preguntas</v>
       </c>
-      <c r="J26" s="272"/>
-      <c r="K26" s="270" t="str">
+      <c r="J26" s="248"/>
+      <c r="K26" s="246" t="str">
         <f ca="1">'Datos RC'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>2 Preguntas</v>
       </c>
-      <c r="L26" s="271"/>
-      <c r="M26" s="270" t="str">
+      <c r="L26" s="247"/>
+      <c r="M26" s="246" t="str">
         <f ca="1">'Datos PP'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>2 Preguntas</v>
       </c>
-      <c r="N26" s="271"/>
-      <c r="O26" s="270" t="str">
+      <c r="N26" s="247"/>
+      <c r="O26" s="246" t="str">
         <f ca="1">'Datos EN'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>2 Preguntas</v>
       </c>
-      <c r="P26" s="271"/>
-      <c r="Q26" s="270" t="str">
+      <c r="P26" s="247"/>
+      <c r="Q26" s="246" t="str">
         <f ca="1">'Datos CL'!G2&amp;" "&amp;INDIRECT("Z_IN_15_"&amp;IDIOMA)</f>
         <v>3 Preguntas</v>
       </c>
-      <c r="R26" s="271"/>
+      <c r="R26" s="247"/>
       <c r="S26" s="6"/>
     </row>
     <row r="27" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="248" t="str">
+      <c r="D27" s="268" t="str">
         <f ca="1">INDIRECT("Z_IN_07_"&amp;IDIOMA)</f>
         <v>Esta HOJA sirve para almacenar las preguntas y poder reutilizarlas cuando sea necesario, sin tener que volver a escribirlas para un nuevo BANCO DE PREGUNTAS.</v>
       </c>
-      <c r="E27" s="248"/>
-      <c r="F27" s="248"/>
-      <c r="G27" s="248"/>
-      <c r="H27" s="248"/>
-      <c r="I27" s="248"/>
-      <c r="J27" s="248"/>
-      <c r="K27" s="248"/>
-      <c r="L27" s="248"/>
-      <c r="M27" s="248"/>
+      <c r="E27" s="268"/>
+      <c r="F27" s="268"/>
+      <c r="G27" s="268"/>
+      <c r="H27" s="268"/>
+      <c r="I27" s="268"/>
+      <c r="J27" s="268"/>
+      <c r="K27" s="268"/>
+      <c r="L27" s="268"/>
+      <c r="M27" s="268"/>
       <c r="N27" s="144"/>
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
@@ -22364,141 +22343,141 @@
     <row r="28" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
-      <c r="F28" s="249"/>
-      <c r="G28" s="249"/>
-      <c r="H28" s="249"/>
-      <c r="I28" s="249"/>
-      <c r="J28" s="249"/>
-      <c r="K28" s="249"/>
-      <c r="L28" s="249"/>
-      <c r="M28" s="249"/>
+      <c r="D28" s="269"/>
+      <c r="E28" s="269"/>
+      <c r="F28" s="269"/>
+      <c r="G28" s="269"/>
+      <c r="H28" s="269"/>
+      <c r="I28" s="269"/>
+      <c r="J28" s="269"/>
+      <c r="K28" s="269"/>
+      <c r="L28" s="269"/>
+      <c r="M28" s="269"/>
       <c r="N28" s="145"/>
       <c r="O28" s="5"/>
-      <c r="P28" s="250"/>
-      <c r="Q28" s="250"/>
-      <c r="R28" s="250"/>
+      <c r="P28" s="245"/>
+      <c r="Q28" s="245"/>
+      <c r="R28" s="245"/>
       <c r="S28" s="6"/>
     </row>
     <row r="29" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="249"/>
-      <c r="E29" s="249"/>
-      <c r="F29" s="249"/>
-      <c r="G29" s="249"/>
-      <c r="H29" s="249"/>
-      <c r="I29" s="249"/>
-      <c r="J29" s="249"/>
-      <c r="K29" s="249"/>
-      <c r="L29" s="249"/>
-      <c r="M29" s="249"/>
+      <c r="D29" s="269"/>
+      <c r="E29" s="269"/>
+      <c r="F29" s="269"/>
+      <c r="G29" s="269"/>
+      <c r="H29" s="269"/>
+      <c r="I29" s="269"/>
+      <c r="J29" s="269"/>
+      <c r="K29" s="269"/>
+      <c r="L29" s="269"/>
+      <c r="M29" s="269"/>
       <c r="N29" s="145"/>
       <c r="O29" s="5"/>
-      <c r="P29" s="250"/>
-      <c r="Q29" s="250"/>
-      <c r="R29" s="250"/>
+      <c r="P29" s="245"/>
+      <c r="Q29" s="245"/>
+      <c r="R29" s="245"/>
       <c r="S29" s="6"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="249"/>
-      <c r="E30" s="249"/>
-      <c r="F30" s="249"/>
-      <c r="G30" s="249"/>
-      <c r="H30" s="249"/>
-      <c r="I30" s="249"/>
-      <c r="J30" s="249"/>
-      <c r="K30" s="249"/>
-      <c r="L30" s="249"/>
-      <c r="M30" s="249"/>
+      <c r="D30" s="269"/>
+      <c r="E30" s="269"/>
+      <c r="F30" s="269"/>
+      <c r="G30" s="269"/>
+      <c r="H30" s="269"/>
+      <c r="I30" s="269"/>
+      <c r="J30" s="269"/>
+      <c r="K30" s="269"/>
+      <c r="L30" s="269"/>
+      <c r="M30" s="269"/>
       <c r="N30" s="145"/>
       <c r="O30" s="5"/>
-      <c r="P30" s="250"/>
-      <c r="Q30" s="250"/>
-      <c r="R30" s="250"/>
+      <c r="P30" s="245"/>
+      <c r="Q30" s="245"/>
+      <c r="R30" s="245"/>
       <c r="S30" s="6"/>
     </row>
     <row r="31" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="249"/>
-      <c r="E31" s="249"/>
-      <c r="F31" s="249"/>
-      <c r="G31" s="249"/>
-      <c r="H31" s="249"/>
-      <c r="I31" s="249"/>
-      <c r="J31" s="249"/>
-      <c r="K31" s="249"/>
-      <c r="L31" s="249"/>
-      <c r="M31" s="249"/>
+      <c r="D31" s="269"/>
+      <c r="E31" s="269"/>
+      <c r="F31" s="269"/>
+      <c r="G31" s="269"/>
+      <c r="H31" s="269"/>
+      <c r="I31" s="269"/>
+      <c r="J31" s="269"/>
+      <c r="K31" s="269"/>
+      <c r="L31" s="269"/>
+      <c r="M31" s="269"/>
       <c r="N31" s="145"/>
       <c r="O31" s="5"/>
-      <c r="P31" s="250"/>
-      <c r="Q31" s="250"/>
-      <c r="R31" s="250"/>
+      <c r="P31" s="245"/>
+      <c r="Q31" s="245"/>
+      <c r="R31" s="245"/>
       <c r="S31" s="6"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="249"/>
-      <c r="E32" s="249"/>
-      <c r="F32" s="249"/>
-      <c r="G32" s="249"/>
-      <c r="H32" s="249"/>
-      <c r="I32" s="249"/>
-      <c r="J32" s="249"/>
-      <c r="K32" s="249"/>
-      <c r="L32" s="249"/>
-      <c r="M32" s="249"/>
+      <c r="D32" s="269"/>
+      <c r="E32" s="269"/>
+      <c r="F32" s="269"/>
+      <c r="G32" s="269"/>
+      <c r="H32" s="269"/>
+      <c r="I32" s="269"/>
+      <c r="J32" s="269"/>
+      <c r="K32" s="269"/>
+      <c r="L32" s="269"/>
+      <c r="M32" s="269"/>
       <c r="N32" s="145"/>
       <c r="O32" s="5"/>
-      <c r="P32" s="250"/>
-      <c r="Q32" s="250"/>
-      <c r="R32" s="250"/>
+      <c r="P32" s="245"/>
+      <c r="Q32" s="245"/>
+      <c r="R32" s="245"/>
       <c r="S32" s="6"/>
     </row>
     <row r="33" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="249"/>
-      <c r="E33" s="249"/>
-      <c r="F33" s="249"/>
-      <c r="G33" s="249"/>
-      <c r="H33" s="249"/>
-      <c r="I33" s="249"/>
-      <c r="J33" s="249"/>
-      <c r="K33" s="249"/>
-      <c r="L33" s="249"/>
-      <c r="M33" s="249"/>
+      <c r="D33" s="269"/>
+      <c r="E33" s="269"/>
+      <c r="F33" s="269"/>
+      <c r="G33" s="269"/>
+      <c r="H33" s="269"/>
+      <c r="I33" s="269"/>
+      <c r="J33" s="269"/>
+      <c r="K33" s="269"/>
+      <c r="L33" s="269"/>
+      <c r="M33" s="269"/>
       <c r="N33" s="145"/>
       <c r="O33" s="5"/>
-      <c r="P33" s="250"/>
-      <c r="Q33" s="250"/>
-      <c r="R33" s="250"/>
+      <c r="P33" s="245"/>
+      <c r="Q33" s="245"/>
+      <c r="R33" s="245"/>
       <c r="S33" s="6"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="249"/>
-      <c r="E34" s="249"/>
-      <c r="F34" s="249"/>
-      <c r="G34" s="249"/>
-      <c r="H34" s="249"/>
-      <c r="I34" s="249"/>
-      <c r="J34" s="249"/>
-      <c r="K34" s="249"/>
-      <c r="L34" s="249"/>
-      <c r="M34" s="249"/>
+      <c r="D34" s="269"/>
+      <c r="E34" s="269"/>
+      <c r="F34" s="269"/>
+      <c r="G34" s="269"/>
+      <c r="H34" s="269"/>
+      <c r="I34" s="269"/>
+      <c r="J34" s="269"/>
+      <c r="K34" s="269"/>
+      <c r="L34" s="269"/>
+      <c r="M34" s="269"/>
       <c r="N34" s="145"/>
       <c r="O34" s="5"/>
-      <c r="P34" s="250"/>
-      <c r="Q34" s="250"/>
-      <c r="R34" s="250"/>
+      <c r="P34" s="245"/>
+      <c r="Q34" s="245"/>
+      <c r="R34" s="245"/>
       <c r="S34" s="6"/>
     </row>
     <row r="35" spans="1:19" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -22613,34 +22592,8 @@
     </row>
     <row r="47" spans="1:19" ht="5.0999999999999996" customHeight="1" thickTop="1" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="B4ZtyPI8lv6/MGOS3+9a5fUlVKn8W7m5tc5qom7GwcpKDO4mxFaT3Eq647jn8+lsT+zoaLPf06hAUqFkuo98DA==" saltValue="Oavj1BI2LOGiAwJ94csGEA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Kr1Ulq79+ug09UOXG724wN4R3pEdg+bpWie2uDMaXA4C7FxidM1FRQ56w5gtkCh77knggDXPPLo56PtbNLJiqA==" saltValue="oP1qBz0l5gUe4ep1gFzpEw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="42">
-    <mergeCell ref="P28:R29"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:F25"/>
-    <mergeCell ref="G24:H25"/>
-    <mergeCell ref="I24:J25"/>
-    <mergeCell ref="K24:L25"/>
-    <mergeCell ref="O24:P25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B1:S1"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="D11:R21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="N5:O10"/>
-    <mergeCell ref="F5:G10"/>
-    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A1:A9"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A17:A19"/>
@@ -22657,8 +22610,34 @@
     <mergeCell ref="Q23:R23"/>
     <mergeCell ref="M24:N25"/>
     <mergeCell ref="Q24:R25"/>
+    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="D11:R21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="N5:O10"/>
+    <mergeCell ref="F5:G10"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="P28:R29"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:F25"/>
+    <mergeCell ref="G24:H25"/>
+    <mergeCell ref="I24:J25"/>
+    <mergeCell ref="K24:L25"/>
+    <mergeCell ref="O24:P25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A11:A13" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$A$39:$A$46</formula1>
     </dataValidation>
@@ -22681,7 +22660,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Hoja_50"/>
   <dimension ref="A1:BF382"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" zeroHeight="1" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" zeroHeight="1" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10.64453125" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="2" max="3" width="6" hidden="1" customWidth="1" outlineLevel="1"/>
@@ -27836,7 +27815,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja_21"/>
   <dimension ref="A1:AI7"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -27920,7 +27899,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!C24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - OPCIÓN MÚLTIPLE 1R 
+        <v>FastTest PlugIn - V8.3 - 0OPCIÓN MÚLTIPLE 1R 
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -28139,46 +28118,46 @@
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
+        <v>831</v>
+      </c>
+      <c r="F5" s="76" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="G5" s="12" t="s">
         <v>833</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>834</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>835</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="K5" s="16" t="s">
         <v>837</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="L5" s="17" t="s">
         <v>838</v>
       </c>
-      <c r="L5" s="17" t="s">
+      <c r="M5" s="24" t="s">
         <v>839</v>
       </c>
-      <c r="M5" s="24" t="s">
+      <c r="N5" s="25" t="s">
         <v>840</v>
       </c>
-      <c r="N5" s="25" t="s">
+      <c r="O5" s="26" t="s">
         <v>841</v>
       </c>
-      <c r="O5" s="26" t="s">
+      <c r="P5" s="27" t="s">
         <v>842</v>
       </c>
-      <c r="P5" s="27" t="s">
+      <c r="Q5" s="28" t="s">
         <v>843</v>
       </c>
-      <c r="Q5" s="28" t="s">
+      <c r="R5" s="29" t="s">
         <v>844</v>
-      </c>
-      <c r="R5" s="29" t="s">
-        <v>845</v>
       </c>
       <c r="S5" s="24">
         <v>100</v>
@@ -28211,39 +28190,38 @@
       <c r="AI5" s="86"/>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.5">
-      <c r="A6" s="276">
+      <c r="A6" s="150">
         <f>IF(COUNTIF(Tabla_OM[[#This Row],[Puntos 1]:[Puntos 6]],"&gt;0")=0,"",COUNTIF(Tabla_OM[[#This Row],[Puntos 1]:[Puntos 6]],"&gt;0"))</f>
         <v>1</v>
       </c>
-      <c r="B6" s="276">
+      <c r="B6" s="150">
         <f>IF(Tabla_OM[[#This Row],[NRC]]="","",COUNTA(Tabla_OM[[#This Row],[Respuesta 1]:[Respuesta 6]])-Tabla_OM[[#This Row],[NRC]])</f>
         <v>5</v>
       </c>
-      <c r="C6" s="277"/>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
+        <v>845</v>
+      </c>
+      <c r="F6" s="76" t="s">
         <v>846</v>
       </c>
-      <c r="F6" s="76" t="s">
+      <c r="G6" s="12" t="s">
         <v>847</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>848</v>
-      </c>
       <c r="H6" s="13" t="s">
-        <v>849</v>
+        <v>965</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>850</v>
+        <v>966</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>851</v>
+        <v>967</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>852</v>
+        <v>968</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>853</v>
+        <v>969</v>
       </c>
       <c r="M6" s="24">
         <v>1</v>
@@ -28284,30 +28262,29 @@
       <c r="AI6" s="86"/>
     </row>
     <row r="7" spans="1:35" ht="35" x14ac:dyDescent="0.5">
-      <c r="A7" s="276">
+      <c r="A7" s="150">
         <f>IF(COUNTIF(Tabla_OM[[#This Row],[Puntos 1]:[Puntos 6]],"&gt;0")=0,"",COUNTIF(Tabla_OM[[#This Row],[Puntos 1]:[Puntos 6]],"&gt;0"))</f>
         <v>1</v>
       </c>
-      <c r="B7" s="276">
+      <c r="B7" s="150">
         <f>IF(Tabla_OM[[#This Row],[NRC]]="","",COUNTA(Tabla_OM[[#This Row],[Respuesta 1]:[Respuesta 6]])-Tabla_OM[[#This Row],[NRC]])</f>
         <v>2</v>
       </c>
-      <c r="C7" s="277"/>
       <c r="D7" s="23"/>
       <c r="E7" s="77" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="16"/>
@@ -28353,7 +28330,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Hoja_22"/>
   <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -28437,7 +28414,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!E24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - OPCIÓN MÚLTIPLE +R 
+        <v>FastTest PlugIn - V8.3 - 0OPCIÓN MÚLTIPLE +R 
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -28660,46 +28637,46 @@
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
+        <v>831</v>
+      </c>
+      <c r="F5" s="76" t="s">
         <v>832</v>
       </c>
-      <c r="F5" s="76" t="s">
-        <v>833</v>
-      </c>
       <c r="G5" s="12" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="I5" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="J5" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="K5" s="16" t="s">
         <v>837</v>
       </c>
-      <c r="K5" s="16" t="s">
-        <v>838</v>
-      </c>
       <c r="L5" s="17" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="M5" s="24" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N5" s="25" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O5" s="26" t="s">
+        <v>841</v>
+      </c>
+      <c r="P5" s="27" t="s">
         <v>842</v>
       </c>
-      <c r="P5" s="27" t="s">
+      <c r="Q5" s="28" t="s">
         <v>843</v>
       </c>
-      <c r="Q5" s="28" t="s">
+      <c r="R5" s="29" t="s">
         <v>844</v>
-      </c>
-      <c r="R5" s="29" t="s">
-        <v>845</v>
       </c>
       <c r="S5" s="24">
         <v>50</v>
@@ -28711,7 +28688,9 @@
       <c r="V5" s="27"/>
       <c r="W5" s="28"/>
       <c r="X5" s="29"/>
-      <c r="Y5" s="199"/>
+      <c r="Y5" s="199">
+        <v>2</v>
+      </c>
       <c r="Z5" s="29"/>
       <c r="AA5" s="29"/>
       <c r="AB5" s="29"/>
@@ -28724,57 +28703,56 @@
       <c r="AI5" s="86"/>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.5">
-      <c r="A6" s="278">
+      <c r="A6" s="150">
         <f>IF(COUNTIF(Tabla_O2[[#This Row],[Puntos 1]:[Puntos 6]],"&gt;0")=0,"",COUNTIF(Tabla_O2[[#This Row],[Puntos 1]:[Puntos 6]],"&gt;0"))</f>
         <v>2</v>
       </c>
-      <c r="B6" s="278">
+      <c r="B6" s="150">
         <f>IF(Tabla_O2[[#This Row],[NRC]]="","",COUNTA(Tabla_O2[[#This Row],[Respuesta 1]:[Respuesta 6]])-Tabla_O2[[#This Row],[NRC]])</f>
         <v>4</v>
       </c>
-      <c r="C6" s="277"/>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
+        <v>845</v>
+      </c>
+      <c r="F6" s="151" t="s">
         <v>846</v>
       </c>
-      <c r="F6" s="151" t="s">
+      <c r="G6" s="12" t="s">
         <v>847</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>848</v>
-      </c>
       <c r="H6" s="13" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>849</v>
+        <v>965</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>850</v>
+        <v>966</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>862</v>
+        <v>970</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>863</v>
+        <v>971</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O6" s="26" t="s">
+        <v>841</v>
+      </c>
+      <c r="P6" s="27" t="s">
         <v>842</v>
       </c>
-      <c r="P6" s="27" t="s">
+      <c r="Q6" s="28" t="s">
         <v>843</v>
       </c>
-      <c r="Q6" s="28" t="s">
+      <c r="R6" s="29" t="s">
         <v>844</v>
-      </c>
-      <c r="R6" s="29" t="s">
-        <v>845</v>
       </c>
       <c r="S6" s="24">
         <v>50</v>
@@ -28812,7 +28790,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Hoja_23"/>
   <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -28889,7 +28867,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!G24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - VERDADERO/FALSO
+        <v>FastTest PlugIn - V8.3 - 0VERDADERO/FALSO
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="67" t="str">
@@ -29058,19 +29036,19 @@
       <c r="B5" s="172"/>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>864</v>
-      </c>
-      <c r="G5" s="12" t="b">
-        <v>1</v>
+        <v>856</v>
+      </c>
+      <c r="G5" s="244" t="s">
+        <v>188</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="J5" s="27"/>
       <c r="K5" s="28"/>
@@ -29108,24 +29086,23 @@
       <c r="AI5" s="66"/>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.5">
-      <c r="A6" s="279"/>
-      <c r="B6" s="279"/>
-      <c r="C6" s="277"/>
+      <c r="A6" s="172"/>
+      <c r="B6" s="172"/>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>868</v>
-      </c>
-      <c r="G6" s="12" t="b">
-        <v>0</v>
+        <v>860</v>
+      </c>
+      <c r="G6" s="244" t="s">
+        <v>195</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="J6" s="27"/>
       <c r="K6" s="28"/>
@@ -29176,7 +29153,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Hoja_24"/>
   <dimension ref="A1:AI7"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -29257,7 +29234,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!I24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - EMPAREJAR
+        <v>FastTest PlugIn - V8.3 - 0EMPAREJAR
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="103" t="str">
@@ -29492,82 +29469,82 @@
       <c r="B5" s="173"/>
       <c r="D5" s="23"/>
       <c r="E5" s="77" t="s">
+        <v>863</v>
+      </c>
+      <c r="F5" s="76" t="s">
+        <v>864</v>
+      </c>
+      <c r="G5" s="87" t="s">
+        <v>865</v>
+      </c>
+      <c r="H5" s="87" t="s">
+        <v>866</v>
+      </c>
+      <c r="I5" s="88" t="s">
+        <v>867</v>
+      </c>
+      <c r="J5" s="88" t="s">
+        <v>868</v>
+      </c>
+      <c r="K5" s="89" t="s">
+        <v>869</v>
+      </c>
+      <c r="L5" s="89" t="s">
+        <v>870</v>
+      </c>
+      <c r="M5" s="90" t="s">
         <v>871</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="N5" s="90" t="s">
         <v>872</v>
       </c>
-      <c r="G5" s="87" t="s">
+      <c r="O5" s="91" t="s">
         <v>873</v>
       </c>
-      <c r="H5" s="87" t="s">
+      <c r="P5" s="91" t="s">
         <v>874</v>
       </c>
-      <c r="I5" s="88" t="s">
+      <c r="Q5" s="92" t="s">
         <v>875</v>
       </c>
-      <c r="J5" s="88" t="s">
+      <c r="R5" s="92" t="s">
         <v>876</v>
       </c>
-      <c r="K5" s="89" t="s">
+      <c r="S5" s="87" t="s">
         <v>877</v>
       </c>
-      <c r="L5" s="89" t="s">
+      <c r="T5" s="87" t="s">
         <v>878</v>
       </c>
-      <c r="M5" s="90" t="s">
+      <c r="U5" s="88" t="s">
         <v>879</v>
       </c>
-      <c r="N5" s="90" t="s">
+      <c r="V5" s="88" t="s">
         <v>880</v>
       </c>
-      <c r="O5" s="91" t="s">
+      <c r="W5" s="89" t="s">
         <v>881</v>
       </c>
-      <c r="P5" s="91" t="s">
+      <c r="X5" s="89" t="s">
         <v>882</v>
       </c>
-      <c r="Q5" s="92" t="s">
+      <c r="Y5" s="90" t="s">
         <v>883</v>
       </c>
-      <c r="R5" s="92" t="s">
+      <c r="Z5" s="90" t="s">
         <v>884</v>
       </c>
-      <c r="S5" s="87" t="s">
+      <c r="AA5" s="91" t="s">
         <v>885</v>
       </c>
-      <c r="T5" s="87" t="s">
+      <c r="AB5" s="91" t="s">
         <v>886</v>
       </c>
-      <c r="U5" s="88" t="s">
+      <c r="AC5" s="92" t="s">
         <v>887</v>
       </c>
-      <c r="V5" s="88" t="s">
+      <c r="AD5" s="92" t="s">
         <v>888</v>
-      </c>
-      <c r="W5" s="89" t="s">
-        <v>889</v>
-      </c>
-      <c r="X5" s="89" t="s">
-        <v>890</v>
-      </c>
-      <c r="Y5" s="90" t="s">
-        <v>891</v>
-      </c>
-      <c r="Z5" s="90" t="s">
-        <v>892</v>
-      </c>
-      <c r="AA5" s="91" t="s">
-        <v>893</v>
-      </c>
-      <c r="AB5" s="91" t="s">
-        <v>894</v>
-      </c>
-      <c r="AC5" s="92" t="s">
-        <v>895</v>
-      </c>
-      <c r="AD5" s="92" t="s">
-        <v>896</v>
       </c>
       <c r="AE5" s="30" t="s">
         <v>275</v>
@@ -29579,95 +29556,94 @@
         <v>277</v>
       </c>
       <c r="AH5" s="33" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="AI5" s="86"/>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.5">
-      <c r="A6" s="280">
+      <c r="A6" s="62">
         <f>IF(COUNTA(Tabla_EM[[#This Row],[Pareja  01.1]:[Pareja  12.14]])/2=0,"",COUNTA(Tabla_EM[[#This Row],[Pareja  01.1]:[Pareja  12.14]])/2)</f>
         <v>12</v>
       </c>
-      <c r="B6" s="281"/>
-      <c r="C6" s="277"/>
+      <c r="B6" s="243"/>
       <c r="D6" s="23"/>
       <c r="E6" s="77" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G6" s="87">
         <v>1</v>
       </c>
       <c r="H6" s="87" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="I6" s="88">
         <v>2</v>
       </c>
       <c r="J6" s="88" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="K6" s="89">
         <v>3</v>
       </c>
       <c r="L6" s="89" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="M6" s="90">
         <v>4</v>
       </c>
       <c r="N6" s="90" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="O6" s="91">
         <v>5</v>
       </c>
       <c r="P6" s="91" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="Q6" s="92">
         <v>6</v>
       </c>
       <c r="R6" s="92" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="S6" s="87">
         <v>7</v>
       </c>
       <c r="T6" s="87" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="U6" s="88">
         <v>8</v>
       </c>
       <c r="V6" s="88" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="W6" s="89">
         <v>9</v>
       </c>
       <c r="X6" s="89" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="Y6" s="90">
         <v>10</v>
       </c>
       <c r="Z6" s="90" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="AA6" s="91">
         <v>11</v>
       </c>
       <c r="AB6" s="91" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="AC6" s="92">
         <v>12</v>
       </c>
       <c r="AD6" s="92" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="AE6" s="93" t="s">
         <v>275</v>
@@ -29679,95 +29655,94 @@
         <v>277</v>
       </c>
       <c r="AH6" s="96" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="AI6" s="86"/>
     </row>
     <row r="7" spans="1:35" ht="143.35" x14ac:dyDescent="0.5">
-      <c r="A7" s="280">
+      <c r="A7" s="62">
         <f>IF(COUNTA(Tabla_EM[[#This Row],[Pareja  01.1]:[Pareja  12.14]])/2=0,"",COUNTA(Tabla_EM[[#This Row],[Pareja  01.1]:[Pareja  12.14]])/2)</f>
         <v>12</v>
       </c>
-      <c r="B7" s="281"/>
-      <c r="C7" s="277"/>
+      <c r="B7" s="243"/>
       <c r="D7" s="23"/>
       <c r="E7" s="77" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G7" s="87" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="H7" s="87" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="I7" s="88" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="J7" s="88" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="K7" s="89" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="L7" s="89" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="M7" s="90" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="N7" s="90" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="O7" s="91" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="P7" s="91" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="Q7" s="92" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="R7" s="92" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="S7" s="87" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="T7" s="87" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="U7" s="88" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="V7" s="88" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="W7" s="89" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="X7" s="89" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="Y7" s="90" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="Z7" s="90" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="AA7" s="91" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="AB7" s="91" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="AC7" s="92" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="AD7" s="92" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="AE7" s="93" t="s">
         <v>275</v>
@@ -29779,7 +29754,7 @@
         <v>277</v>
       </c>
       <c r="AH7" s="96" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="AI7" s="86"/>
     </row>
@@ -29797,7 +29772,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Hoja_25"/>
   <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.64453125" style="2" customWidth="1"/>
     <col min="2" max="2" width="3.64453125" style="2" hidden="1" customWidth="1"/>
@@ -29887,7 +29862,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!K24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - RESPUESTA CORTA
+        <v>FastTest PlugIn - V8.3 - 0RESPUESTA CORTA
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="103" t="str">
@@ -30126,99 +30101,99 @@
         <v>1</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="G5" s="87" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="H5" s="98">
         <v>100</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="J5" s="88" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="K5" s="99">
         <v>100</v>
       </c>
       <c r="L5" s="99" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="M5" s="88" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="N5" s="99">
         <v>100</v>
       </c>
       <c r="O5" s="99" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="P5" s="90" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="Q5" s="100">
         <v>100</v>
       </c>
       <c r="R5" s="100" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="S5" s="91" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="T5" s="101">
         <v>100</v>
       </c>
       <c r="U5" s="101" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="V5" s="92" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="W5" s="102">
         <v>100</v>
       </c>
       <c r="X5" s="102" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="Y5" s="87" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="Z5" s="98">
         <v>100</v>
       </c>
       <c r="AA5" s="98" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="AB5" s="88" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="AC5" s="99">
         <v>100</v>
       </c>
       <c r="AD5" s="99" t="s">
+        <v>915</v>
+      </c>
+      <c r="AE5" s="93" t="s">
         <v>923</v>
       </c>
-      <c r="AE5" s="93" t="s">
-        <v>931</v>
-      </c>
       <c r="AF5" s="94" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="AG5" s="95" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="AH5" s="96" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="AI5" s="86"/>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.5">
-      <c r="A6" s="282">
+      <c r="A6" s="63">
         <f>IF(COUNTA(Tabl_RC[[#This Row],[Respuesta 01]],Tabl_RC[[#This Row],[Respuesta 02]],Tabl_RC[[#This Row],[Respuesta 03]],Tabl_RC[[#This Row],[Respuesta 04]],Tabl_RC[[#This Row],[Respuesta 05]],Tabl_RC[[#This Row],[Respuesta 06]],Tabl_RC[[#This Row],[Respuesta 07]],Tabl_RC[[#This Row],[Respuesta 08]])=0,"",
        COUNTA(Tabl_RC[[#This Row],[Respuesta 01]],Tabl_RC[[#This Row],[Respuesta 02]],Tabl_RC[[#This Row],[Respuesta 03]],Tabl_RC[[#This Row],[Respuesta 04]],Tabl_RC[[#This Row],[Respuesta 05]],Tabl_RC[[#This Row],[Respuesta 06]],Tabl_RC[[#This Row],[Respuesta 07]],Tabl_RC[[#This Row],[Respuesta 08]]))</f>
         <v>3</v>
@@ -30229,37 +30204,37 @@
         <v>0</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="G6" s="87" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="H6" s="98">
         <v>100</v>
       </c>
       <c r="I6" s="98" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="J6" s="88" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="K6" s="99">
         <v>50</v>
       </c>
       <c r="L6" s="99" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="M6" s="88" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="N6" s="99">
         <v>100</v>
       </c>
       <c r="O6" s="99" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="P6" s="90"/>
       <c r="Q6" s="100"/>
@@ -30296,7 +30271,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Hoja_26"/>
   <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -30377,7 +30352,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!M24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - PALABRA PERDIDA
+        <v>FastTest PlugIn - V8.3 - 0PALABRA PERDIDA
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="117" t="str">
@@ -30637,194 +30612,194 @@
       <c r="C5" s="152"/>
       <c r="D5" s="152"/>
       <c r="E5" s="119" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="F5" s="151" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="G5" s="12">
         <v>1</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="I5" s="13">
         <v>1</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="K5" s="12">
         <v>1</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="M5" s="13">
         <v>1</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="O5" s="12">
         <v>2</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="Q5" s="13">
         <v>2</v>
       </c>
       <c r="R5" s="13" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="S5" s="12">
         <v>2</v>
       </c>
       <c r="T5" s="12" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="U5" s="13">
         <v>3</v>
       </c>
       <c r="V5" s="13" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="W5" s="12">
         <v>3</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="Y5" s="13">
         <v>3</v>
       </c>
       <c r="Z5" s="13" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="AA5" s="12">
         <v>3</v>
       </c>
       <c r="AB5" s="12" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AC5" s="13">
         <v>3</v>
       </c>
       <c r="AD5" s="13" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AE5" s="153" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AF5" s="154" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="AG5" s="155" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="AH5" s="156" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="AI5" s="86"/>
     </row>
     <row r="6" spans="1:35" ht="35" x14ac:dyDescent="0.5">
-      <c r="A6" s="280">
+      <c r="A6" s="62">
         <f>IF(COUNTA(Tabla_PP[[#This Row],[GP 01]:[P 12]])/2=0,"",COUNTA(Tabla_PP[[#This Row],[GP 01]:[P 12]])/2)</f>
         <v>12</v>
       </c>
-      <c r="B6" s="283"/>
+      <c r="B6" s="11"/>
       <c r="C6" s="152"/>
       <c r="D6" s="152"/>
       <c r="E6" s="119" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="F6" s="151" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="G6" s="12">
         <v>1</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="I6" s="13">
         <v>1</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="K6" s="12">
         <v>1</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="M6" s="13">
         <v>1</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="O6" s="12">
         <v>2</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="Q6" s="13">
         <v>2</v>
       </c>
       <c r="R6" s="13" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="S6" s="12">
         <v>2</v>
       </c>
       <c r="T6" s="12" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="U6" s="13">
         <v>3</v>
       </c>
       <c r="V6" s="13" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="W6" s="12">
         <v>3</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="Y6" s="13">
         <v>3</v>
       </c>
       <c r="Z6" s="13" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="AA6" s="12">
         <v>3</v>
       </c>
       <c r="AB6" s="12" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="AC6" s="13">
         <v>3</v>
       </c>
       <c r="AD6" s="13" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AE6" s="153" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AF6" s="154" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="AG6" s="155" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="AH6" s="156" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="AI6" s="86"/>
     </row>
@@ -30842,7 +30817,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Hoja_27"/>
   <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -30926,7 +30901,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!O24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - ENSAYO
+        <v>FastTest PlugIn - V8.3 - 0ENSAYO
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="55" t="str">
@@ -31098,27 +31073,27 @@
       <c r="C5" s="152"/>
       <c r="D5" s="152"/>
       <c r="E5" s="119" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="F5" s="151" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="G5" s="128" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="H5" s="25"/>
       <c r="I5" s="14">
         <v>5</v>
       </c>
       <c r="J5" s="129" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="K5" s="130"/>
       <c r="L5" s="131" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="M5" s="128" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="N5" s="157"/>
       <c r="O5" s="158"/>
@@ -31144,21 +31119,21 @@
       <c r="AI5" s="86"/>
     </row>
     <row r="6" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
-      <c r="A6" s="284"/>
-      <c r="B6" s="285"/>
+      <c r="A6" s="175"/>
+      <c r="B6" s="176"/>
       <c r="C6" s="152"/>
       <c r="D6" s="152"/>
       <c r="E6" s="119" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="F6" s="151" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="G6" s="128" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="I6" s="14">
         <v>5</v>
@@ -31167,13 +31142,13 @@
         <v>3</v>
       </c>
       <c r="K6" s="130" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="L6" s="131" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="M6" s="128" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="N6" s="157"/>
       <c r="O6" s="158"/>
@@ -31220,7 +31195,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Hoja_28"/>
   <dimension ref="A1:AI7"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="3.64453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="3.52734375" hidden="1" customWidth="1"/>
@@ -31287,8 +31262,8 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="275"/>
-      <c r="B3" s="275"/>
+      <c r="A3" s="277"/>
+      <c r="B3" s="277"/>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
       <c r="E3" s="22" t="str">
@@ -31298,7 +31273,7 @@
       <c r="F3" s="36" t="str">
         <f ca="1">"FastTest PlugIn - V"&amp;MID(Version,5,7)&amp;UPPER(INICIO!Q24)&amp;"
 "&amp;INDIRECT("Z_BP_03_"&amp;IDIOMA)</f>
-        <v>FastTest PlugIn - V7.8  - CLOZE
+        <v>FastTest PlugIn - V8.3 - 0CLOZE
 Enunciado de la pregunta</v>
       </c>
       <c r="G3" s="133" t="str">
@@ -31465,10 +31440,10 @@
       <c r="C5" s="152"/>
       <c r="D5" s="152"/>
       <c r="E5" s="77" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="F5" s="151" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="G5" s="163">
         <v>5</v>
@@ -31505,15 +31480,15 @@
       <c r="AI5" s="86"/>
     </row>
     <row r="6" spans="1:35" ht="81.7" x14ac:dyDescent="0.5">
-      <c r="A6" s="284"/>
-      <c r="B6" s="285"/>
+      <c r="A6" s="175"/>
+      <c r="B6" s="176"/>
       <c r="C6" s="152"/>
       <c r="D6" s="152"/>
       <c r="E6" s="77" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="F6" s="151" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="G6" s="163">
         <v>15</v>
@@ -31544,31 +31519,31 @@
       <c r="AC6" s="157"/>
       <c r="AD6" s="157"/>
       <c r="AE6" s="164" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="AF6" s="165" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="AG6" s="166" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="AH6" s="167" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="AI6" s="86" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="23.35" x14ac:dyDescent="0.5">
-      <c r="A7" s="284"/>
-      <c r="B7" s="285"/>
+      <c r="A7" s="175"/>
+      <c r="B7" s="176"/>
       <c r="C7" s="152"/>
       <c r="D7" s="152"/>
       <c r="E7" s="77" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
       <c r="F7" s="151" t="s">
-        <v>971</v>
+        <v>962</v>
       </c>
       <c r="G7" s="163">
         <v>15</v>
@@ -31603,7 +31578,7 @@
       <c r="AI7" s="86"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VkMO1aGRxWdXapAKKFiGj/gtr+VpC8qf2jW69x0tJhbufHK5dvYlfv85rLoh8p4stPlG2TujnJxl0CUVct5r+Q==" saltValue="Fk9YFWFIan3xDNBU602abg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="1">
     <mergeCell ref="A3:B3"/>
   </mergeCells>
